--- a/upload/previsao_renuncias_pre_existentes.xlsx
+++ b/upload/previsao_renuncias_pre_existentes.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$P$99</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="38">
   <si>
     <t>ano</t>
   </si>
@@ -118,6 +118,30 @@
   <si>
     <t>Contribuites Não inscrito</t>
   </si>
+  <si>
+    <t>norma_autorizadora</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 23.685, 07/08/2020</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.831, 28/07/2021</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.218, 15/07/2022</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.404, de 02/08/2023</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.945, de 02/08/2024</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 25.440, de 06/08/2025</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 23.364, de 25/07/2019</t>
+  </si>
 </sst>
 </file>
 
@@ -169,11 +193,14 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,25 +483,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="2"/>
     <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,41 +512,44 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2026</v>
       </c>
@@ -528,32 +559,35 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="3">
         <v>28758214.218902048</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>102005797.61096737</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="3">
         <v>1545863.0138565479</v>
       </c>
-      <c r="J2" s="3">
+      <c r="K2" s="3">
         <v>11781393.300000099</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="3">
         <v>5044081.425784451</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="3">
         <v>786474.38756619033</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>124140.95</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="3">
         <v>45798.2400000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2026</v>
       </c>
@@ -563,41 +597,44 @@
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3">
         <v>210461712.98350856</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="3">
         <v>94622956.646007702</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>2312429.6837642989</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>6549321458.4329481</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>159191916.28537723</v>
       </c>
-      <c r="I3" s="3">
+      <c r="J3" s="3">
         <v>10153727.538947878</v>
       </c>
-      <c r="J3" s="3">
+      <c r="K3" s="3">
         <v>168819138.199999</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>53181091.435577087</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="3">
         <v>2733651452.0807543</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>2647021.16000003</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="3">
         <v>1040548.26</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2026</v>
       </c>
@@ -607,14 +644,17 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3">
         <v>80139518.276975349</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>5412366.2599999998</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2026</v>
       </c>
@@ -624,29 +664,32 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="3">
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3">
         <v>799377378.85826254</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>2342155.1877762354</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>557576.82122012135</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>41987256.660000399</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>8506471.8844920173</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>13609722.907918142</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>308833.3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2026</v>
       </c>
@@ -656,26 +699,29 @@
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="D6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="3">
         <v>111523509.51900658</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>4645.2434847661898</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>12738488.77</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>5834056.5119515946</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>2939027.3850399628</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>37394.04</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2026</v>
       </c>
@@ -685,35 +731,38 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3">
         <v>28369602.880602211</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>217112.83106587079</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>547838794.16420805</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>1168003.1438491158</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>47593.142164313416</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>15144704.3199999</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>6518346.0481342943</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>20425843.843658924</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>368951.43</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2026</v>
       </c>
@@ -723,35 +772,38 @@
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3">
         <v>160844.87165276569</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>798534225.06535351</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8109788.8746463479</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>281265.71481134789</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41939517.449999899</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17995957.445303526</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6227204.2781468071</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>148129.07</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13573.32</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2026</v>
       </c>
@@ -761,35 +813,38 @@
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3">
         <v>89471.222586631513</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1114733.8314280785</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>224554422.02536488</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1320005.3692042606</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11490123.039999999</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6579261.0511011444</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2504881.0873000002</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>118507.78</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3602.76</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2026</v>
       </c>
@@ -799,26 +854,29 @@
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="3">
         <v>263872281.54698476</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>121967.68732163949</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15497108.75</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3600120.2350609428</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1966742.783147715</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>169953.08</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2026</v>
       </c>
@@ -828,29 +886,32 @@
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="3">
         <v>2691.9814157522405</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>6067254751.0023689</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>2944975.7395908581</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>27601000.420000099</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>7013494.8832955174</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>7384148.6085253386</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>173295.24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2026</v>
       </c>
@@ -860,26 +921,29 @@
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="3">
         <v>55386896.974768952</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>55903.777409881586</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9238840.6099999696</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5208292.3220345182</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1748278.413153809</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>77735.62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2026</v>
       </c>
@@ -889,29 +953,32 @@
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="3">
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="3">
         <v>179850.08940810547</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>1144915208.4210625</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>2209602.2176256124</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>52887714.6599999</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>3281881.4073480447</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>3320108.807376693</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>169895.75</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>2026</v>
       </c>
@@ -921,35 +988,38 @@
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="3">
         <v>85397.099629493328</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10634637.42064655</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1723781414.847378</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4256808.7024897849</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>31172719.3400001</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4719611.762255962</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7336152.6658894103</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>482730.06999999902</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2348.7600000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2026</v>
       </c>
@@ -959,32 +1029,35 @@
       <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="3">
         <v>1632070394.9289515</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1675435.6683833969</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18646.245223174566</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27582272.68</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12332805.886891188</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5113859.2046221457</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>469771.26</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>850.1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2025</v>
       </c>
@@ -994,35 +1067,38 @@
       <c r="C16" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3">
         <v>66863912</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>21836</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
         <v>195422978</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>2032982</v>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
         <v>19355847</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
         <v>1084236</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>122430</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>50434</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2025</v>
       </c>
@@ -1032,39 +1108,42 @@
       <c r="C17" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3">
         <v>222083075</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136201401</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2001731</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6017632097</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>116787627</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7668463</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>284159654</v>
       </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3">
+      <c r="L17" s="3"/>
+      <c r="M17" s="3">
         <v>3810866064</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2651062</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1968491</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2025</v>
       </c>
@@ -1074,25 +1153,28 @@
       <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="3">
         <v>60527622</v>
       </c>
-      <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
         <v>10250999</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>201722838</v>
       </c>
-      <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2025</v>
       </c>
@@ -1102,37 +1184,40 @@
       <c r="C19" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="3">
         <v>48790</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>103713813</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3">
         <v>838489375</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>1992605</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>18022</v>
       </c>
-      <c r="J19" s="3">
+      <c r="K19" s="3">
         <v>64932602</v>
       </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3">
         <v>20625652</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>213704</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>132357</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2025</v>
       </c>
@@ -1142,35 +1227,38 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3">
         <v>5575080</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3">
         <v>96513205</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8540</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18348775</v>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3">
         <v>4133455</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>53946</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1270</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2025</v>
       </c>
@@ -1180,37 +1268,40 @@
       <c r="C21" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3">
         <v>32230905</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>335014</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
         <v>599604954</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3605746</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>158840</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28823085</v>
       </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3">
+      <c r="L21" s="3"/>
+      <c r="M21" s="3">
         <v>23708809</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>135348</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21520</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2025</v>
       </c>
@@ -1220,37 +1311,40 @@
       <c r="C22" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="3">
         <v>791242</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>370922</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
         <v>810871554</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9703838</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>40598</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54695594</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3">
+      <c r="L22" s="3"/>
+      <c r="M22" s="3">
         <v>8831272</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>160094</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13573</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2025</v>
       </c>
@@ -1260,37 +1354,40 @@
       <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3">
         <v>412140</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>976917</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
         <v>273260680</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>495151</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20043481</v>
       </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3">
+      <c r="L23" s="3"/>
+      <c r="M23" s="3">
         <v>4322454</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>110518</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2041</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2025</v>
       </c>
@@ -1300,35 +1397,38 @@
       <c r="C24" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
         <v>25416086</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
         <v>189253991</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>65624</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32520889</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3">
+      <c r="L24" s="3"/>
+      <c r="M24" s="3">
         <v>3610612</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>248961</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2025</v>
       </c>
@@ -1338,37 +1438,40 @@
       <c r="C25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3">
         <v>1670065</v>
       </c>
-      <c r="E25" s="3">
+      <c r="F25" s="3">
         <v>284226</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3">
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
         <v>4631582591</v>
       </c>
-      <c r="H25" s="3">
+      <c r="I25" s="3">
         <v>2683559</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="J25" s="3">
+      <c r="K25" s="3">
         <v>53112391</v>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3">
+      <c r="L25" s="3"/>
+      <c r="M25" s="3">
         <v>12027875</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>159691</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O25" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2025</v>
       </c>
@@ -1378,33 +1481,36 @@
       <c r="C26" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3">
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
         <v>60208032</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16012</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>0</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13030386</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3">
+      <c r="L26" s="3"/>
+      <c r="M26" s="3">
         <v>3292090</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>71318</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>596</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2025</v>
       </c>
@@ -1414,37 +1520,40 @@
       <c r="C27" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="3">
         <v>32717</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>540926</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3">
+      <c r="G27" s="3"/>
+      <c r="H27" s="3">
         <v>943448160</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1558689</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>0</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>68174858</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3">
+      <c r="L27" s="3"/>
+      <c r="M27" s="3">
         <v>10739986</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>346401</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5559</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2025</v>
       </c>
@@ -1454,37 +1563,40 @@
       <c r="C28" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="3">
         <v>30556</v>
       </c>
-      <c r="E28" s="3">
+      <c r="F28" s="3">
         <v>51969477</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3">
         <v>1041216868</v>
       </c>
-      <c r="H28" s="3">
+      <c r="I28" s="3">
         <v>4404679</v>
       </c>
-      <c r="I28" s="3">
+      <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="J28" s="3">
+      <c r="K28" s="3">
         <v>48292411</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3">
+      <c r="L28" s="3"/>
+      <c r="M28" s="3">
         <v>12506535</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>408098</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="3">
         <v>2349</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2025</v>
       </c>
@@ -1494,37 +1606,40 @@
       <c r="C29" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="3">
         <v>377967.163</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>165992</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3">
+      <c r="G29" s="3"/>
+      <c r="H29" s="3">
         <v>1223121608</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>788532</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>12383</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>46769686</v>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3">
+      <c r="L29" s="3"/>
+      <c r="M29" s="3">
         <v>10281421</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>231979</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>1020</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2024</v>
       </c>
@@ -1534,35 +1649,38 @@
       <c r="C30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="3">
         <v>74837512</v>
       </c>
-      <c r="E30" s="3">
+      <c r="F30" s="3">
         <v>4398090</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3">
+      <c r="G30" s="3"/>
+      <c r="H30" s="3">
         <v>357509869</v>
       </c>
-      <c r="H30" s="3">
+      <c r="I30" s="3">
         <v>9986153</v>
       </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3">
+      <c r="J30" s="3"/>
+      <c r="K30" s="3">
         <v>10962289</v>
       </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3">
+      <c r="L30" s="3"/>
+      <c r="M30" s="3">
         <v>671704</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>20275</v>
       </c>
-      <c r="N30" s="3">
+      <c r="O30" s="3">
         <v>4641</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2024</v>
       </c>
@@ -1572,39 +1690,42 @@
       <c r="C31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="3">
         <v>118377731</v>
       </c>
-      <c r="E31" s="3">
+      <c r="F31" s="3">
         <v>360311824</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <v>1899874</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>4192019706</v>
       </c>
-      <c r="H31" s="3">
+      <c r="I31" s="3">
         <v>85737225</v>
       </c>
-      <c r="I31" s="3">
+      <c r="J31" s="3">
         <v>7004345</v>
       </c>
-      <c r="J31" s="3">
+      <c r="K31" s="3">
         <v>91528260</v>
       </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3">
+      <c r="L31" s="3"/>
+      <c r="M31" s="3">
         <v>2634739970</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>2262590</v>
       </c>
-      <c r="N31" s="3">
+      <c r="O31" s="3">
         <v>2038214</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2024</v>
       </c>
@@ -1614,25 +1735,28 @@
       <c r="C32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="3">
         <v>65707878</v>
       </c>
-      <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3">
+      <c r="J32" s="3"/>
+      <c r="K32" s="3">
         <v>1857564</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>63238777</v>
       </c>
-      <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2024</v>
       </c>
@@ -1642,37 +1766,40 @@
       <c r="C33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="3">
         <v>141200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>109107652</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
         <v>559956624</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3875525</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>479482</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14248902</v>
       </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3">
+      <c r="L33" s="3"/>
+      <c r="M33" s="3">
         <v>15938291</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>55669</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14520</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2024</v>
       </c>
@@ -1682,31 +1809,34 @@
       <c r="C34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3">
+      <c r="D34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
         <v>42436818</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3">
         <v>67130001</v>
       </c>
-      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3">
         <v>6484400</v>
       </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3">
+      <c r="L34" s="3"/>
+      <c r="M34" s="3">
         <v>2316756</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>17694</v>
       </c>
-      <c r="N34" s="3">
+      <c r="O34" s="3">
         <v>6252</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2024</v>
       </c>
@@ -1716,35 +1846,38 @@
       <c r="C35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="3">
         <v>4314767</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6784862</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3">
+      <c r="G35" s="3"/>
+      <c r="H35" s="3">
         <v>741281914</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23183686</v>
       </c>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3">
         <v>10038204</v>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3">
+      <c r="L35" s="3"/>
+      <c r="M35" s="3">
         <v>14263308</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>80226</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34523</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2024</v>
       </c>
@@ -1754,37 +1887,40 @@
       <c r="C36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="3">
         <v>1462624</v>
       </c>
-      <c r="E36" s="3">
+      <c r="F36" s="3">
         <v>13024528</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3">
+      <c r="G36" s="3"/>
+      <c r="H36" s="3">
         <v>508531790</v>
       </c>
-      <c r="H36" s="3">
+      <c r="I36" s="3">
         <v>10323020</v>
       </c>
-      <c r="I36" s="3">
+      <c r="J36" s="3">
         <v>6226</v>
       </c>
-      <c r="J36" s="3">
+      <c r="K36" s="3">
         <v>26873220</v>
       </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3">
+      <c r="L36" s="3"/>
+      <c r="M36" s="3">
         <v>6024453</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>124404</v>
       </c>
-      <c r="N36" s="3">
+      <c r="O36" s="3">
         <v>19542</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2024</v>
       </c>
@@ -1794,33 +1930,36 @@
       <c r="C37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3">
+      <c r="D37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3">
         <v>2122934</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3">
+      <c r="G37" s="3"/>
+      <c r="H37" s="3">
         <v>213729585</v>
       </c>
-      <c r="H37" s="3">
+      <c r="I37" s="3">
         <v>366192</v>
       </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3">
+      <c r="J37" s="3"/>
+      <c r="K37" s="3">
         <v>6835493</v>
       </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3">
+      <c r="L37" s="3"/>
+      <c r="M37" s="3">
         <v>2911811</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>94368</v>
       </c>
-      <c r="N37" s="3">
+      <c r="O37" s="3">
         <v>5535</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2024</v>
       </c>
@@ -1830,35 +1969,38 @@
       <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="3">
         <v>520</v>
       </c>
-      <c r="E38" s="3">
+      <c r="F38" s="3">
         <v>2590584</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3">
+      <c r="G38" s="3"/>
+      <c r="H38" s="3">
         <v>287468234</v>
       </c>
-      <c r="H38" s="3">
+      <c r="I38" s="3">
         <v>511826</v>
       </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3">
+      <c r="J38" s="3"/>
+      <c r="K38" s="3">
         <v>3983291</v>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3">
+      <c r="L38" s="3"/>
+      <c r="M38" s="3">
         <v>2545310</v>
       </c>
-      <c r="M38" s="3">
+      <c r="N38" s="3">
         <v>153663</v>
       </c>
-      <c r="N38" s="3">
+      <c r="O38" s="3">
         <v>2780</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2024</v>
       </c>
@@ -1868,35 +2010,38 @@
       <c r="C39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="3">
         <v>1987359</v>
       </c>
-      <c r="E39" s="3">
+      <c r="F39" s="3">
         <v>4159638</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3">
+      <c r="G39" s="3"/>
+      <c r="H39" s="3">
         <v>3473539356</v>
       </c>
-      <c r="H39" s="3">
+      <c r="I39" s="3">
         <v>25822759</v>
       </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3">
+      <c r="J39" s="3"/>
+      <c r="K39" s="3">
         <v>11061936</v>
       </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3">
         <v>6857377</v>
       </c>
-      <c r="M39" s="3">
+      <c r="N39" s="3">
         <v>116222</v>
       </c>
-      <c r="N39" s="3">
+      <c r="O39" s="3">
         <v>238</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2024</v>
       </c>
@@ -1906,33 +2051,36 @@
       <c r="C40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3">
+      <c r="D40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3">
         <v>501831</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3">
         <v>47897254</v>
       </c>
-      <c r="H40" s="3">
+      <c r="I40" s="3">
         <v>350483</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3">
+      <c r="J40" s="3"/>
+      <c r="K40" s="3">
         <v>5040526</v>
       </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3">
         <v>1938892</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="3">
         <v>54026</v>
       </c>
-      <c r="N40" s="3">
+      <c r="O40" s="3">
         <v>1193</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2024</v>
       </c>
@@ -1942,35 +2090,38 @@
       <c r="C41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="3">
         <v>88799</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2517949</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3">
+      <c r="G41" s="3"/>
+      <c r="H41" s="3">
         <v>1053546964</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1026263</v>
       </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3">
+      <c r="J41" s="3"/>
+      <c r="K41" s="3">
         <v>11156143</v>
       </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3">
+      <c r="L41" s="3"/>
+      <c r="M41" s="3">
         <v>9343016</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>269278</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5836</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2024</v>
       </c>
@@ -1980,35 +2131,38 @@
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="3">
         <v>1176</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37255466</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3">
+      <c r="G42" s="3"/>
+      <c r="H42" s="3">
         <v>862951688</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3560014</v>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3">
+      <c r="J42" s="3"/>
+      <c r="K42" s="3">
         <v>13588461</v>
       </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3">
+      <c r="L42" s="3"/>
+      <c r="M42" s="3">
         <v>7820957</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>282384</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>379</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2024</v>
       </c>
@@ -2018,37 +2172,40 @@
       <c r="C43" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="3">
         <v>503.55360000000002</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2951609</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3">
+      <c r="G43" s="3"/>
+      <c r="H43" s="3">
         <v>1025550947</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>722717</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10771</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14986382</v>
       </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3">
+      <c r="L43" s="3"/>
+      <c r="M43" s="3">
         <v>5677235</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>137848</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7395</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2023</v>
       </c>
@@ -2058,31 +2215,34 @@
       <c r="C44" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3">
+      <c r="D44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
         <v>3109360</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3">
+      <c r="G44" s="3"/>
+      <c r="H44" s="3">
         <v>332089092</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8652542</v>
       </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3">
+      <c r="J44" s="3"/>
+      <c r="K44" s="3">
         <v>11820609</v>
       </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3">
+      <c r="L44" s="3"/>
+      <c r="M44" s="3">
         <v>269310</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19372</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2023</v>
       </c>
@@ -2092,39 +2252,42 @@
       <c r="C45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="3">
         <v>3034118</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>326628553</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2304833</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3673054888</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27663343</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18993546</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>128925260</v>
       </c>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3">
+      <c r="L45" s="3"/>
+      <c r="M45" s="3">
         <v>1419389361</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1752976</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1997819</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2023</v>
       </c>
@@ -2134,27 +2297,30 @@
       <c r="C46" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="3">
         <v>46893592</v>
       </c>
-      <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3">
+      <c r="J46" s="3"/>
+      <c r="K46" s="3">
         <v>1896979</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51708325</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>126338</v>
       </c>
-      <c r="M46" s="3"/>
       <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2023</v>
       </c>
@@ -2164,37 +2330,40 @@
       <c r="C47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="3">
         <v>4527</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>88921885</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3">
+      <c r="G47" s="3"/>
+      <c r="H47" s="3">
         <v>738658715</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1388980</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>533552</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>35163854</v>
       </c>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3">
+      <c r="L47" s="3"/>
+      <c r="M47" s="3">
         <v>9389001</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>67670</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14628</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2023</v>
       </c>
@@ -2204,33 +2373,36 @@
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3">
+      <c r="D48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3">
         <v>19143188</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3">
+      <c r="G48" s="3"/>
+      <c r="H48" s="3">
         <v>106318247</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>58559</v>
       </c>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3">
+      <c r="J48" s="3"/>
+      <c r="K48" s="3">
         <v>8519021</v>
       </c>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3">
+      <c r="L48" s="3"/>
+      <c r="M48" s="3">
         <v>1189992</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14957</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4695</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2023</v>
       </c>
@@ -2240,33 +2412,36 @@
       <c r="C49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3">
+      <c r="D49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
         <v>6910631</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3">
+      <c r="G49" s="3"/>
+      <c r="H49" s="3">
         <v>1029511355</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18425482</v>
       </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3">
+      <c r="J49" s="3"/>
+      <c r="K49" s="3">
         <v>12845481</v>
       </c>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3">
+      <c r="L49" s="3"/>
+      <c r="M49" s="3">
         <v>8263906</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30907</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34523</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2023</v>
       </c>
@@ -2276,37 +2451,40 @@
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="3">
         <v>353632</v>
       </c>
-      <c r="E50" s="3">
+      <c r="F50" s="3">
         <v>12332475</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3">
+      <c r="G50" s="3"/>
+      <c r="H50" s="3">
         <v>626574301</v>
       </c>
-      <c r="H50" s="3">
+      <c r="I50" s="3">
         <v>8472046</v>
       </c>
-      <c r="I50" s="3">
+      <c r="J50" s="3">
         <v>50218</v>
       </c>
-      <c r="J50" s="3">
+      <c r="K50" s="3">
         <v>34534827</v>
       </c>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3">
+      <c r="L50" s="3"/>
+      <c r="M50" s="3">
         <v>2266983</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="3">
         <v>141130</v>
       </c>
-      <c r="N50" s="3">
+      <c r="O50" s="3">
         <v>13309</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2023</v>
       </c>
@@ -2316,31 +2494,34 @@
       <c r="C51" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3">
+      <c r="D51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
         <v>2079787</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3">
+      <c r="G51" s="3"/>
+      <c r="H51" s="3">
         <v>184444495</v>
       </c>
-      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3">
+      <c r="J51" s="3"/>
+      <c r="K51" s="3">
         <v>8849090</v>
       </c>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3">
+      <c r="L51" s="3"/>
+      <c r="M51" s="3">
         <v>7319370</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>92181</v>
       </c>
-      <c r="N51" s="3">
+      <c r="O51" s="3">
         <v>18966</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2023</v>
       </c>
@@ -2350,33 +2531,36 @@
       <c r="C52" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3">
+      <c r="D52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
         <v>2954780</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3">
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
         <v>253859129</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>380840</v>
       </c>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3">
+      <c r="J52" s="3"/>
+      <c r="K52" s="3">
         <v>7548076</v>
       </c>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3">
+      <c r="L52" s="3"/>
+      <c r="M52" s="3">
         <v>1609297</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>144977</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6161</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2023</v>
       </c>
@@ -2386,33 +2570,36 @@
       <c r="C53" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3">
+      <c r="D53" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
         <v>2327777</v>
       </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
+      <c r="G53" s="3"/>
+      <c r="H53" s="3">
         <v>3409258736</v>
       </c>
-      <c r="H53" s="3">
+      <c r="I53" s="3">
         <v>19892394</v>
       </c>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3">
+      <c r="J53" s="3"/>
+      <c r="K53" s="3">
         <v>16430355</v>
       </c>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3">
+      <c r="L53" s="3"/>
+      <c r="M53" s="3">
         <v>3468121</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="3">
         <v>88285</v>
       </c>
-      <c r="N53" s="3">
+      <c r="O53" s="3">
         <v>26621</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2023</v>
       </c>
@@ -2422,33 +2609,36 @@
       <c r="C54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3">
+      <c r="D54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3">
         <v>466424</v>
       </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3">
+      <c r="G54" s="3"/>
+      <c r="H54" s="3">
         <v>41679777</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>110000</v>
       </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3">
+      <c r="J54" s="3"/>
+      <c r="K54" s="3">
         <v>7846231</v>
       </c>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3">
+      <c r="L54" s="3"/>
+      <c r="M54" s="3">
         <v>669042</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55559</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4617</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>2023</v>
       </c>
@@ -2458,33 +2648,36 @@
       <c r="C55" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3">
+      <c r="D55" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3">
         <v>2246582</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3">
+      <c r="G55" s="3"/>
+      <c r="H55" s="3">
         <v>7184916667</v>
       </c>
-      <c r="H55" s="3">
+      <c r="I55" s="3">
         <v>735931</v>
       </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3">
+      <c r="J55" s="3"/>
+      <c r="K55" s="3">
         <v>15998576</v>
       </c>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3">
         <v>6310450</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="3">
         <v>293148</v>
       </c>
-      <c r="N55" s="3">
+      <c r="O55" s="3">
         <v>5985</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>2023</v>
       </c>
@@ -2494,33 +2687,36 @@
       <c r="C56" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3">
+      <c r="D56" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3">
         <v>21183486</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3">
+      <c r="G56" s="3"/>
+      <c r="H56" s="3">
         <v>846551045</v>
       </c>
-      <c r="H56" s="3">
+      <c r="I56" s="3">
         <v>6789179</v>
       </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3">
+      <c r="J56" s="3"/>
+      <c r="K56" s="3">
         <v>24677989</v>
       </c>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3">
         <v>3389193</v>
       </c>
-      <c r="M56" s="3">
+      <c r="N56" s="3">
         <v>100316</v>
       </c>
-      <c r="N56" s="3">
+      <c r="O56" s="3">
         <v>2330</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>2023</v>
       </c>
@@ -2530,35 +2726,38 @@
       <c r="C57" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3">
+      <c r="D57" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3">
         <v>2123416</v>
       </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3">
+      <c r="G57" s="3"/>
+      <c r="H57" s="3">
         <v>987858845</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>350649</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14545</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24677501</v>
       </c>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3">
+      <c r="L57" s="3"/>
+      <c r="M57" s="3">
         <v>2855410</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>130285</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7268</v>
       </c>
     </row>
-    <row r="58" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>2022</v>
       </c>
@@ -2568,29 +2767,32 @@
       <c r="C58" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E58" s="3">
+      <c r="D58" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="3">
         <v>1244476</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>596657526</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5606781</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1229359</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>242932</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>43951</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>292</v>
       </c>
     </row>
-    <row r="59" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>2022</v>
       </c>
@@ -2600,38 +2802,41 @@
       <c r="C59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="3">
         <v>2100415</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>129874495</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2368591</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1658446843</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23965439</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3948954</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>288984553</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>953576930</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1901039</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1959250</v>
       </c>
     </row>
-    <row r="60" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>2022</v>
       </c>
@@ -2641,23 +2846,26 @@
       <c r="C60" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" s="3">
         <v>26927812</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2815</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2240179</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47809190</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23104280</v>
       </c>
     </row>
-    <row r="61" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>2022</v>
       </c>
@@ -2667,35 +2875,38 @@
       <c r="C61" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" s="3">
         <v>7179</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>85572913</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>660690621</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3122346</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>537027</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24863232</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4851787</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50621</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22697</v>
       </c>
     </row>
-    <row r="62" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>2022</v>
       </c>
@@ -2705,29 +2916,32 @@
       <c r="C62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="D62" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" s="3">
         <v>18266095</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>257602026</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1386</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3471956</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>792384</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16386</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7981</v>
       </c>
     </row>
-    <row r="63" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>2022</v>
       </c>
@@ -2737,32 +2951,35 @@
       <c r="C63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" s="3">
         <v>958036</v>
       </c>
-      <c r="E63" s="3">
+      <c r="F63" s="3">
         <v>4089302</v>
       </c>
-      <c r="G63" s="3">
+      <c r="H63" s="3">
         <v>418653174</v>
       </c>
-      <c r="H63" s="3">
+      <c r="I63" s="3">
         <v>14151282</v>
       </c>
-      <c r="J63" s="3">
+      <c r="K63" s="3">
         <v>6972822</v>
       </c>
-      <c r="L63" s="3">
+      <c r="M63" s="3">
         <v>6676000</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="3">
         <v>33295</v>
       </c>
-      <c r="N63" s="3">
+      <c r="O63" s="3">
         <v>34717</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2022</v>
       </c>
@@ -2772,35 +2989,38 @@
       <c r="C64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E64" s="3">
         <v>51939</v>
       </c>
-      <c r="E64" s="3">
+      <c r="F64" s="3">
         <v>7799075</v>
       </c>
-      <c r="G64" s="3">
+      <c r="H64" s="3">
         <v>683034366</v>
       </c>
-      <c r="H64" s="3">
+      <c r="I64" s="3">
         <v>8875734</v>
       </c>
-      <c r="I64" s="3">
+      <c r="J64" s="3">
         <v>23863</v>
       </c>
-      <c r="J64" s="3">
+      <c r="K64" s="3">
         <v>9763939</v>
       </c>
-      <c r="L64" s="3">
+      <c r="M64" s="3">
         <v>1997322</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="3">
         <v>109476</v>
       </c>
-      <c r="N64" s="3">
+      <c r="O64" s="3">
         <v>17638</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>2022</v>
       </c>
@@ -2810,32 +3030,35 @@
       <c r="C65" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="3">
         <v>81</v>
       </c>
-      <c r="E65" s="3">
+      <c r="F65" s="3">
         <v>1320555</v>
       </c>
-      <c r="G65" s="3">
+      <c r="H65" s="3">
         <v>320943320</v>
       </c>
-      <c r="H65" s="3">
+      <c r="I65" s="3">
         <v>12176</v>
       </c>
-      <c r="J65" s="3">
+      <c r="K65" s="3">
         <v>3931679</v>
       </c>
-      <c r="L65" s="3">
+      <c r="M65" s="3">
         <v>2980794</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="3">
         <v>112305</v>
       </c>
-      <c r="N65" s="3">
+      <c r="O65" s="3">
         <v>15668</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>2022</v>
       </c>
@@ -2845,32 +3068,35 @@
       <c r="C66" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" s="3">
         <v>4656215</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24489716</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>448757970</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>551921</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>994936</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>696242</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>91016</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9358</v>
       </c>
     </row>
-    <row r="67" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>2022</v>
       </c>
@@ -2880,29 +3106,32 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="3">
+      <c r="D67" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" s="3">
         <v>37857420</v>
       </c>
-      <c r="G67" s="3">
+      <c r="H67" s="3">
         <v>2721008942</v>
       </c>
-      <c r="H67" s="3">
+      <c r="I67" s="3">
         <v>15772093</v>
       </c>
-      <c r="J67" s="3">
+      <c r="K67" s="3">
         <v>5525156</v>
       </c>
-      <c r="L67" s="3">
+      <c r="M67" s="3">
         <v>1559226</v>
       </c>
-      <c r="M67" s="3">
+      <c r="N67" s="3">
         <v>88434</v>
       </c>
-      <c r="N67" s="3">
+      <c r="O67" s="3">
         <v>40065</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>2022</v>
       </c>
@@ -2912,32 +3141,35 @@
       <c r="C68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" s="3">
         <v>5186</v>
       </c>
-      <c r="E68" s="3">
+      <c r="F68" s="3">
         <v>337315</v>
       </c>
-      <c r="G68" s="3">
+      <c r="H68" s="3">
         <v>81373189</v>
       </c>
-      <c r="H68" s="3">
+      <c r="I68" s="3">
         <v>5000</v>
       </c>
-      <c r="J68" s="3">
+      <c r="K68" s="3">
         <v>1711602</v>
       </c>
-      <c r="L68" s="3">
+      <c r="M68" s="3">
         <v>307834</v>
       </c>
-      <c r="M68" s="3">
+      <c r="N68" s="3">
         <v>44998</v>
       </c>
-      <c r="N68" s="3">
+      <c r="O68" s="3">
         <v>4929</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>2022</v>
       </c>
@@ -2947,32 +3179,35 @@
       <c r="C69" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" s="3">
         <v>47702973</v>
       </c>
-      <c r="E69" s="3">
+      <c r="F69" s="3">
         <v>2997656</v>
       </c>
-      <c r="G69" s="3">
+      <c r="H69" s="3">
         <v>512852361</v>
       </c>
-      <c r="H69" s="3">
+      <c r="I69" s="3">
         <v>963053</v>
       </c>
-      <c r="J69" s="3">
+      <c r="K69" s="3">
         <v>11509072</v>
       </c>
-      <c r="L69" s="3">
+      <c r="M69" s="3">
         <v>2831260</v>
       </c>
-      <c r="M69" s="3">
+      <c r="N69" s="3">
         <v>256191</v>
       </c>
-      <c r="N69" s="3">
+      <c r="O69" s="3">
         <v>6419</v>
       </c>
     </row>
-    <row r="70" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>2022</v>
       </c>
@@ -2982,29 +3217,32 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="3">
+      <c r="D70" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" s="3">
         <v>30656406</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>760956847</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>5310420</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>7231020</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1588268</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>172228</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1573</v>
       </c>
     </row>
-    <row r="71" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>2022</v>
       </c>
@@ -3014,32 +3252,35 @@
       <c r="C71" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="3">
+      <c r="D71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" s="3">
         <v>1810768</v>
       </c>
-      <c r="G71" s="3">
+      <c r="H71" s="3">
         <v>729547178</v>
       </c>
-      <c r="H71" s="3">
+      <c r="I71" s="3">
         <v>1088393</v>
       </c>
-      <c r="I71" s="3">
+      <c r="J71" s="3">
         <v>20188</v>
       </c>
-      <c r="J71" s="3">
+      <c r="K71" s="3">
         <v>4329638</v>
       </c>
-      <c r="L71" s="3">
+      <c r="M71" s="3">
         <v>1398751</v>
       </c>
-      <c r="M71" s="3">
+      <c r="N71" s="3">
         <v>148804</v>
       </c>
-      <c r="N71" s="3">
+      <c r="O71" s="3">
         <v>6106</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>2021</v>
       </c>
@@ -3049,34 +3290,37 @@
       <c r="C72" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3">
+      <c r="D72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3">
         <v>1307436</v>
       </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3">
+      <c r="G72" s="3"/>
+      <c r="H72" s="3">
         <v>102587876</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2370607</v>
       </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3">
         <v>4013675</v>
       </c>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3">
+      <c r="L72" s="3"/>
+      <c r="M72" s="3">
         <v>384703</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30720</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3631</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>2021</v>
       </c>
@@ -3086,40 +3330,43 @@
       <c r="C73" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="3">
         <v>384998</v>
       </c>
-      <c r="E73" s="3">
+      <c r="F73" s="3">
         <v>238370388</v>
       </c>
-      <c r="F73" s="3">
+      <c r="G73" s="3">
         <v>1279016</v>
       </c>
-      <c r="G73" s="3">
+      <c r="H73" s="3">
         <v>1762665757</v>
       </c>
-      <c r="H73" s="3">
+      <c r="I73" s="3">
         <v>29453254</v>
       </c>
-      <c r="I73" s="3">
+      <c r="J73" s="3">
         <v>2506874</v>
       </c>
-      <c r="J73" s="3">
+      <c r="K73" s="3">
         <v>375027725</v>
       </c>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3">
+      <c r="L73" s="3"/>
+      <c r="M73" s="3">
         <v>1018298448</v>
       </c>
-      <c r="M73" s="3">
+      <c r="N73" s="3">
         <v>1439863</v>
       </c>
-      <c r="N73" s="3">
+      <c r="O73" s="3">
         <v>212109</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>2021</v>
       </c>
@@ -3129,26 +3376,29 @@
       <c r="C74" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="3">
         <v>20683167</v>
       </c>
-      <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-      <c r="J74" s="3">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3">
         <v>3180002</v>
       </c>
-      <c r="K74" s="3">
+      <c r="L74" s="3">
         <v>44494260</v>
       </c>
-      <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>2021</v>
       </c>
@@ -3158,36 +3408,39 @@
       <c r="C75" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3">
+      <c r="D75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3">
         <v>58872677</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3">
+      <c r="G75" s="3"/>
+      <c r="H75" s="3">
         <v>410808542</v>
       </c>
-      <c r="H75" s="3">
+      <c r="I75" s="3">
         <v>2433658</v>
       </c>
-      <c r="I75" s="3">
+      <c r="J75" s="3">
         <v>294078</v>
       </c>
-      <c r="J75" s="3">
+      <c r="K75" s="3">
         <v>116417529</v>
       </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3">
+      <c r="L75" s="3"/>
+      <c r="M75" s="3">
         <v>3936034</v>
       </c>
-      <c r="M75" s="3">
+      <c r="N75" s="3">
         <v>25539</v>
       </c>
-      <c r="N75" s="3">
+      <c r="O75" s="3">
         <v>16923</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>2021</v>
       </c>
@@ -3197,34 +3450,37 @@
       <c r="C76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3">
+      <c r="D76" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3">
         <v>11481951</v>
       </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3">
+      <c r="G76" s="3"/>
+      <c r="H76" s="3">
         <v>65054029</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20165</v>
       </c>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3">
+      <c r="J76" s="3"/>
+      <c r="K76" s="3">
         <v>5533283</v>
       </c>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3">
+      <c r="L76" s="3"/>
+      <c r="M76" s="3">
         <v>1158981</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18953</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7722</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>2021</v>
       </c>
@@ -3234,36 +3490,39 @@
       <c r="C77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" s="3">
         <v>465428</v>
       </c>
-      <c r="E77" s="3">
+      <c r="F77" s="3">
         <v>5022510</v>
       </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3">
+      <c r="G77" s="3"/>
+      <c r="H77" s="3">
         <v>217528374</v>
       </c>
-      <c r="H77" s="3">
+      <c r="I77" s="3">
         <v>6005517</v>
       </c>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3">
+      <c r="J77" s="3"/>
+      <c r="K77" s="3">
         <v>9751411</v>
       </c>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3">
+      <c r="L77" s="3"/>
+      <c r="M77" s="3">
         <v>5235407</v>
       </c>
-      <c r="M77" s="3">
+      <c r="N77" s="3">
         <v>27076</v>
       </c>
-      <c r="N77" s="3">
+      <c r="O77" s="3">
         <v>516</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P77" s="3"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>2021</v>
       </c>
@@ -3273,36 +3532,39 @@
       <c r="C78" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3">
+      <c r="D78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
         <v>13128934</v>
       </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3">
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
         <v>328238955</v>
       </c>
-      <c r="H78" s="3">
+      <c r="I78" s="3">
         <v>22706918</v>
       </c>
-      <c r="I78" s="3">
+      <c r="J78" s="3">
         <v>46263</v>
       </c>
-      <c r="J78" s="3">
+      <c r="K78" s="3">
         <v>16090748</v>
       </c>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3">
+      <c r="L78" s="3"/>
+      <c r="M78" s="3">
         <v>2939284</v>
       </c>
-      <c r="M78" s="3">
+      <c r="N78" s="3">
         <v>79375</v>
       </c>
-      <c r="N78" s="3">
+      <c r="O78" s="3">
         <v>43817</v>
       </c>
-      <c r="O78" s="3"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P78" s="3"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>2021</v>
       </c>
@@ -3312,34 +3574,37 @@
       <c r="C79" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3">
+      <c r="D79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
         <v>1898560</v>
       </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3">
+      <c r="G79" s="3"/>
+      <c r="H79" s="3">
         <v>124525402</v>
       </c>
-      <c r="H79" s="3">
+      <c r="I79" s="3">
         <v>590904</v>
       </c>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3">
+      <c r="J79" s="3"/>
+      <c r="K79" s="3">
         <v>5402246</v>
       </c>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3">
+      <c r="L79" s="3"/>
+      <c r="M79" s="3">
         <v>2145451</v>
       </c>
-      <c r="M79" s="3">
+      <c r="N79" s="3">
         <v>75520</v>
       </c>
-      <c r="N79" s="3">
+      <c r="O79" s="3">
         <v>28380</v>
       </c>
-      <c r="O79" s="3"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P79" s="3"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>2021</v>
       </c>
@@ -3349,34 +3614,37 @@
       <c r="C80" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3">
+      <c r="D80" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3">
         <v>3077404</v>
       </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3">
         <v>171608308</v>
       </c>
-      <c r="H80" s="3">
+      <c r="I80" s="3">
         <v>1603841</v>
       </c>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3">
+      <c r="J80" s="3"/>
+      <c r="K80" s="3">
         <v>2163979</v>
       </c>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3">
+      <c r="L80" s="3"/>
+      <c r="M80" s="3">
         <v>861713</v>
       </c>
-      <c r="M80" s="3">
+      <c r="N80" s="3">
         <v>37801</v>
       </c>
-      <c r="N80" s="3">
+      <c r="O80" s="3">
         <v>8966</v>
       </c>
-      <c r="O80" s="3"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>2021</v>
       </c>
@@ -3386,34 +3654,37 @@
       <c r="C81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3">
+      <c r="D81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3">
         <v>1607944</v>
       </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3">
+      <c r="G81" s="3"/>
+      <c r="H81" s="3">
         <v>1916376241</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7942866</v>
       </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3">
+      <c r="J81" s="3"/>
+      <c r="K81" s="3">
         <v>7425173</v>
       </c>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3">
+      <c r="L81" s="3"/>
+      <c r="M81" s="3">
         <v>1658891</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>79123</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>40472</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>2021</v>
       </c>
@@ -3423,34 +3694,37 @@
       <c r="C82" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3">
+      <c r="D82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3">
         <v>757721</v>
       </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3">
+      <c r="G82" s="3"/>
+      <c r="H82" s="3">
         <v>57295201</v>
       </c>
-      <c r="H82" s="3">
+      <c r="I82" s="3">
         <v>5231</v>
       </c>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3">
+      <c r="J82" s="3"/>
+      <c r="K82" s="3">
         <v>2658018</v>
       </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3">
         <v>738545</v>
       </c>
-      <c r="M82" s="3">
+      <c r="N82" s="3">
         <v>51424</v>
       </c>
-      <c r="N82" s="3">
+      <c r="O82" s="3">
         <v>5028</v>
       </c>
-      <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>2021</v>
       </c>
@@ -3460,36 +3734,39 @@
       <c r="C83" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" s="3">
         <v>40538310</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1987764</v>
       </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3">
+      <c r="G83" s="3"/>
+      <c r="H83" s="3">
         <v>346900437</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1364202</v>
       </c>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3">
+      <c r="J83" s="3"/>
+      <c r="K83" s="3">
         <v>18463969</v>
       </c>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3">
+      <c r="L83" s="3"/>
+      <c r="M83" s="3">
         <v>1777330</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65485</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1339</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>2021</v>
       </c>
@@ -3499,34 +3776,37 @@
       <c r="C84" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3">
+      <c r="D84" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3">
         <v>27746641</v>
       </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3">
+      <c r="G84" s="3"/>
+      <c r="H84" s="3">
         <v>516664091</v>
       </c>
-      <c r="H84" s="3">
+      <c r="I84" s="3">
         <v>9620860</v>
       </c>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3">
+      <c r="J84" s="3"/>
+      <c r="K84" s="3">
         <v>11396104</v>
       </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3">
+      <c r="L84" s="3"/>
+      <c r="M84" s="3">
         <v>2928124</v>
       </c>
-      <c r="M84" s="3">
+      <c r="N84" s="3">
         <v>173236</v>
       </c>
-      <c r="N84" s="3">
+      <c r="O84" s="3">
         <v>3480</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>2021</v>
       </c>
@@ -3536,36 +3816,39 @@
       <c r="C85" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3">
+      <c r="D85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3">
         <v>1989135</v>
       </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3">
+      <c r="G85" s="3"/>
+      <c r="H85" s="3">
         <v>453554112</v>
       </c>
-      <c r="H85" s="3">
+      <c r="I85" s="3">
         <v>1530383</v>
       </c>
-      <c r="I85" s="3">
+      <c r="J85" s="3">
         <v>7257</v>
       </c>
-      <c r="J85" s="3">
+      <c r="K85" s="3">
         <v>8550440</v>
       </c>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3">
+      <c r="L85" s="3"/>
+      <c r="M85" s="3">
         <v>2360549</v>
       </c>
-      <c r="M85" s="3">
+      <c r="N85" s="3">
         <v>115914</v>
       </c>
-      <c r="N85" s="3">
+      <c r="O85" s="3">
         <v>29846</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>2020</v>
       </c>
@@ -3575,33 +3858,36 @@
       <c r="C86" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E86" s="3">
         <v>1384579</v>
       </c>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3">
         <v>366011668</v>
       </c>
-      <c r="G86" s="3">
+      <c r="H86" s="3">
         <v>5648129</v>
       </c>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3">
+      <c r="I86" s="3"/>
+      <c r="J86" s="3">
         <v>4719631</v>
       </c>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3">
+      <c r="K86" s="3"/>
+      <c r="L86" s="3">
         <v>291433</v>
       </c>
-      <c r="L86" s="3">
+      <c r="M86" s="3">
         <v>8627</v>
       </c>
-      <c r="M86" s="3">
+      <c r="N86" s="3">
         <v>4516</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>2020</v>
       </c>
@@ -3611,37 +3897,40 @@
       <c r="C87" t="s">
         <v>3</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E87" s="3">
         <v>292584631</v>
       </c>
-      <c r="E87" s="3">
+      <c r="F87" s="3">
         <v>1640678</v>
       </c>
-      <c r="F87" s="3">
+      <c r="G87" s="3">
         <v>1372215845</v>
       </c>
-      <c r="G87" s="3">
+      <c r="H87" s="3">
         <v>20120369</v>
       </c>
-      <c r="H87" s="3">
+      <c r="I87" s="3">
         <v>1408572</v>
       </c>
-      <c r="I87" s="3">
+      <c r="J87" s="3">
         <v>410088084</v>
       </c>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3">
+      <c r="K87" s="3"/>
+      <c r="L87" s="3">
         <v>209526319</v>
       </c>
-      <c r="L87" s="3">
+      <c r="M87" s="3">
         <v>1010128</v>
       </c>
-      <c r="M87" s="3">
+      <c r="N87" s="3">
         <v>240243</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>2020</v>
       </c>
@@ -3651,27 +3940,30 @@
       <c r="C88" t="s">
         <v>29</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E88" s="3">
         <v>17112041</v>
       </c>
-      <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="3">
+      <c r="I88" s="3"/>
+      <c r="J88" s="3">
         <v>4335223</v>
       </c>
-      <c r="J88" s="3">
+      <c r="K88" s="3">
         <v>35126368</v>
       </c>
-      <c r="K88" s="3">
+      <c r="L88" s="3">
         <v>300484932</v>
       </c>
-      <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>2020</v>
       </c>
@@ -3681,35 +3973,38 @@
       <c r="C89" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E89" s="3">
         <v>96836704</v>
       </c>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3">
+      <c r="F89" s="3"/>
+      <c r="G89" s="3">
         <v>318670996</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1991862</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>390632</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29036774</v>
       </c>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3">
+      <c r="K89" s="3"/>
+      <c r="L89" s="3">
         <v>1999949</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>59063</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40538</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>2020</v>
       </c>
@@ -3719,33 +4014,36 @@
       <c r="C90" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E90" s="3">
         <v>15473329</v>
       </c>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3">
+      <c r="F90" s="3"/>
+      <c r="G90" s="3">
         <v>46357932</v>
       </c>
-      <c r="G90" s="3">
+      <c r="H90" s="3">
         <v>13497</v>
       </c>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3">
+      <c r="I90" s="3"/>
+      <c r="J90" s="3">
         <v>5699961</v>
       </c>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3">
+      <c r="K90" s="3"/>
+      <c r="L90" s="3">
         <v>354586</v>
       </c>
-      <c r="L90" s="3">
+      <c r="M90" s="3">
         <v>37014</v>
       </c>
-      <c r="M90" s="3">
+      <c r="N90" s="3">
         <v>1693086</v>
       </c>
-      <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>2020</v>
       </c>
@@ -3755,33 +4053,36 @@
       <c r="C91" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E91" s="3">
         <v>2339391</v>
       </c>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3">
+      <c r="F91" s="3"/>
+      <c r="G91" s="3">
         <v>242475609</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>5910644</v>
       </c>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3">
+      <c r="I91" s="3"/>
+      <c r="J91" s="3">
         <v>11195928</v>
       </c>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3">
+      <c r="K91" s="3"/>
+      <c r="L91" s="3">
         <v>2684176</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>31048</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>2284</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>2020</v>
       </c>
@@ -3791,35 +4092,38 @@
       <c r="C92" t="s">
         <v>7</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E92" s="3">
         <v>12547449</v>
       </c>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3">
+      <c r="F92" s="3"/>
+      <c r="G92" s="3">
         <v>286402699</v>
       </c>
-      <c r="G92" s="3">
+      <c r="H92" s="3">
         <v>10381545</v>
       </c>
-      <c r="H92" s="3">
+      <c r="I92" s="3">
         <v>38439</v>
       </c>
-      <c r="I92" s="3">
+      <c r="J92" s="3">
         <v>20896533</v>
       </c>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3">
+      <c r="K92" s="3"/>
+      <c r="L92" s="3">
         <v>725033</v>
       </c>
-      <c r="L92" s="3">
+      <c r="M92" s="3">
         <v>99707</v>
       </c>
-      <c r="M92" s="3">
+      <c r="N92" s="3">
         <v>20414</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>2020</v>
       </c>
@@ -3829,33 +4133,36 @@
       <c r="C93" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" s="3">
         <v>1763550</v>
       </c>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3">
+      <c r="F93" s="3"/>
+      <c r="G93" s="3">
         <v>95232205</v>
       </c>
-      <c r="G93" s="3">
+      <c r="H93" s="3">
         <v>459897</v>
       </c>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3">
+      <c r="I93" s="3"/>
+      <c r="J93" s="3">
         <v>7138953</v>
       </c>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3">
+      <c r="K93" s="3"/>
+      <c r="L93" s="3">
         <v>453092</v>
       </c>
-      <c r="L93" s="3">
+      <c r="M93" s="3">
         <v>41962</v>
       </c>
-      <c r="M93" s="3">
+      <c r="N93" s="3">
         <v>72499</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>2020</v>
       </c>
@@ -3865,33 +4172,36 @@
       <c r="C94" t="s">
         <v>9</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" s="3">
         <v>55207966</v>
       </c>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3">
+      <c r="F94" s="3"/>
+      <c r="G94" s="3">
         <v>112554421</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24528</v>
       </c>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3">
+      <c r="I94" s="3"/>
+      <c r="J94" s="3">
         <v>2611960</v>
       </c>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3">
+      <c r="K94" s="3"/>
+      <c r="L94" s="3">
         <v>124118</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>70586</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7109</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>2020</v>
       </c>
@@ -3901,33 +4211,36 @@
       <c r="C95" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E95" s="3">
         <v>1363050</v>
       </c>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3">
+      <c r="F95" s="3"/>
+      <c r="G95" s="3">
         <v>1692445905</v>
       </c>
-      <c r="G95" s="3">
+      <c r="H95" s="3">
         <v>9584735</v>
       </c>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3">
+      <c r="I95" s="3"/>
+      <c r="J95" s="3">
         <v>12985497</v>
       </c>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3">
+      <c r="K95" s="3"/>
+      <c r="L95" s="3">
         <v>395197</v>
       </c>
-      <c r="L95" s="3">
+      <c r="M95" s="3">
         <v>64001</v>
       </c>
-      <c r="M95" s="3">
+      <c r="N95" s="3">
         <v>43810</v>
       </c>
-      <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>2020</v>
       </c>
@@ -3937,31 +4250,34 @@
       <c r="C96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E96" s="3">
         <v>342096</v>
       </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3">
+      <c r="F96" s="3"/>
+      <c r="G96" s="3">
         <v>19970465</v>
       </c>
-      <c r="G96" s="3"/>
       <c r="H96" s="3"/>
-      <c r="I96" s="3">
+      <c r="I96" s="3"/>
+      <c r="J96" s="3">
         <v>3386428</v>
       </c>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3">
+      <c r="K96" s="3"/>
+      <c r="L96" s="3">
         <v>290871</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>93133</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>5246</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>2020</v>
       </c>
@@ -3971,33 +4287,36 @@
       <c r="C97" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E97" s="3">
         <v>1924558</v>
       </c>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3">
+      <c r="F97" s="3"/>
+      <c r="G97" s="3">
         <v>162382838</v>
       </c>
-      <c r="G97" s="3">
+      <c r="H97" s="3">
         <v>435831</v>
       </c>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3">
+      <c r="I97" s="3"/>
+      <c r="J97" s="3">
         <v>21158700</v>
       </c>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3">
+      <c r="K97" s="3"/>
+      <c r="L97" s="3">
         <v>732568</v>
       </c>
-      <c r="L97" s="3">
+      <c r="M97" s="3">
         <v>26372</v>
       </c>
-      <c r="M97" s="3">
+      <c r="N97" s="3">
         <v>23665</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>2020</v>
       </c>
@@ -4007,33 +4326,36 @@
       <c r="C98" t="s">
         <v>13</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E98" s="3">
         <v>46638689</v>
       </c>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3">
+      <c r="F98" s="3"/>
+      <c r="G98" s="3">
         <v>303595090</v>
       </c>
-      <c r="G98" s="3">
+      <c r="H98" s="3">
         <v>6739767</v>
       </c>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3">
+      <c r="I98" s="3"/>
+      <c r="J98" s="3">
         <v>18773917</v>
       </c>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3">
+      <c r="K98" s="3"/>
+      <c r="L98" s="3">
         <v>173887</v>
       </c>
-      <c r="L98" s="3">
+      <c r="M98" s="3">
         <v>132567</v>
       </c>
-      <c r="M98" s="3">
+      <c r="N98" s="3">
         <v>31622</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>2020</v>
       </c>
@@ -4043,34 +4365,37 @@
       <c r="C99" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E99" s="3">
         <v>687467</v>
       </c>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3">
+      <c r="F99" s="3"/>
+      <c r="G99" s="3">
         <v>374646909</v>
       </c>
-      <c r="G99" s="3">
+      <c r="H99" s="3">
         <v>131285</v>
       </c>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3">
+      <c r="I99" s="3"/>
+      <c r="J99" s="3">
         <v>15753690</v>
       </c>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3">
+      <c r="K99" s="3"/>
+      <c r="L99" s="3">
         <v>707712</v>
       </c>
-      <c r="L99" s="3">
+      <c r="M99" s="3">
         <v>102420</v>
       </c>
-      <c r="M99" s="3">
+      <c r="N99" s="3">
         <v>65106</v>
       </c>
-      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1">
+  <autoFilter ref="A1:P99">
     <sortState ref="A2:O99">
       <sortCondition descending="1" ref="A1"/>
     </sortState>
